--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_Wheel.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_Wheel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3DA3D6-B07E-4E85-AC04-2226CB380741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62856F70-F767-44FD-B149-750462E7894E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="1950" windowWidth="26910" windowHeight="12765" tabRatio="940" activeTab="3" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="6330" yWindow="2205" windowWidth="21600" windowHeight="11295" tabRatio="940" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="RWheel_Hamba_f" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="39">
   <si>
     <t>Units</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>RackWheel_SUV_Landy_f</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -270,7 +276,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -701,7 +763,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -840,480 +902,478 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="11">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0.37675517503754502</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <v>0.92326153885340301</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="11">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.37675517503754502</v>
+      </c>
       <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>0.92326153885340301</v>
+      </c>
+      <c r="K10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="22" t="s">
-        <v>34</v>
+      <c r="H12" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="17">
-        <f t="shared" ref="H13:AB13" si="0">H18*$H$19</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R13" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB13" s="17">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+      <c r="H13" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="16">
-        <f>H16*$H$17</f>
+      <c r="H14" s="17">
+        <f t="shared" ref="H14:AB14" si="0">H19*$H$20</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R14" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB14" s="17">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="16">
+        <f>H17*$H$18</f>
         <v>-0.18</v>
       </c>
-      <c r="I14" s="16">
-        <f t="shared" ref="I14:AB14" si="1">I16*$H$17</f>
+      <c r="I15" s="16">
+        <f t="shared" ref="I15:AB15" si="1">I17*$H$18</f>
         <v>-0.1638</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J15" s="16">
         <f t="shared" si="1"/>
         <v>-0.14616000000000001</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K15" s="16">
         <f t="shared" si="1"/>
         <v>-0.12672</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L15" s="16">
         <f t="shared" si="1"/>
         <v>-0.10668000000000001</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M15" s="16">
         <f t="shared" si="1"/>
         <v>-8.7719999999999992E-2</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N15" s="16">
         <f t="shared" si="1"/>
         <v>-7.0679999999999993E-2</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O15" s="16">
         <f t="shared" si="1"/>
         <v>-5.4719999999999998E-2</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P15" s="16">
         <f t="shared" si="1"/>
         <v>-3.8159999999999999E-2</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q15" s="16">
         <f t="shared" si="1"/>
         <v>-1.9800000000000002E-2</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R15" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S15" s="16">
         <f t="shared" si="1"/>
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T15" s="16">
         <f t="shared" si="1"/>
         <v>3.8159999999999999E-2</v>
       </c>
-      <c r="U14" s="16">
+      <c r="U15" s="16">
         <f t="shared" si="1"/>
         <v>5.4719999999999998E-2</v>
       </c>
-      <c r="V14" s="16">
+      <c r="V15" s="16">
         <f t="shared" si="1"/>
         <v>7.0679999999999993E-2</v>
       </c>
-      <c r="W14" s="16">
+      <c r="W15" s="16">
         <f t="shared" si="1"/>
         <v>8.7780000000000011E-2</v>
       </c>
-      <c r="X14" s="16">
+      <c r="X15" s="16">
         <f t="shared" si="1"/>
         <v>0.10668000000000001</v>
       </c>
-      <c r="Y14" s="16">
+      <c r="Y15" s="16">
         <f t="shared" si="1"/>
         <v>0.12672</v>
       </c>
-      <c r="Z14" s="16">
+      <c r="Z15" s="16">
         <f t="shared" si="1"/>
         <v>0.14616000000000001</v>
       </c>
-      <c r="AA14" s="16">
+      <c r="AA15" s="16">
         <f t="shared" si="1"/>
         <v>0.1638</v>
       </c>
-      <c r="AB14" s="16">
+      <c r="AB15" s="16">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="11">
-        <v>-0.3</v>
-      </c>
-      <c r="I16">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J16">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K16">
-        <v>-0.2112</v>
-      </c>
-      <c r="L16">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M16">
-        <v>-0.1462</v>
-      </c>
-      <c r="N16">
-        <v>-0.1178</v>
-      </c>
-      <c r="O16">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P16">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q16">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T16">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U16">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V16">
-        <v>0.1178</v>
-      </c>
-      <c r="W16">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X16">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y16">
-        <v>0.2112</v>
-      </c>
-      <c r="Z16">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA16">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB16">
-        <v>0.3</v>
-      </c>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17">
+      <c r="H17" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="I17">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J17">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K17">
+        <v>-0.2112</v>
+      </c>
+      <c r="L17">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M17">
+        <v>-0.1462</v>
+      </c>
+      <c r="N17">
+        <v>-0.1178</v>
+      </c>
+      <c r="O17">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P17">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q17">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T17">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U17">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V17">
+        <v>0.1178</v>
+      </c>
+      <c r="W17">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X17">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y17">
+        <v>0.2112</v>
+      </c>
+      <c r="Z17">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA17">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="H18" s="11">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H19" s="11">
         <v>-180</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>-162</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>-144</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>-126</v>
       </c>
-      <c r="L18">
+      <c r="L19">
         <v>-108</v>
       </c>
-      <c r="M18">
+      <c r="M19">
         <v>-90</v>
       </c>
-      <c r="N18">
+      <c r="N19">
         <v>-72</v>
       </c>
-      <c r="O18">
+      <c r="O19">
         <v>-54</v>
       </c>
-      <c r="P18">
+      <c r="P19">
         <v>-36</v>
       </c>
-      <c r="Q18">
+      <c r="Q19">
         <v>-18</v>
       </c>
-      <c r="R18">
+      <c r="R19">
         <v>0</v>
       </c>
-      <c r="S18">
+      <c r="S19">
         <v>18</v>
       </c>
-      <c r="T18">
+      <c r="T19">
         <v>36</v>
       </c>
-      <c r="U18">
+      <c r="U19">
         <v>54</v>
       </c>
-      <c r="V18">
+      <c r="V19">
         <v>72</v>
       </c>
-      <c r="W18">
+      <c r="W19">
         <v>90</v>
       </c>
-      <c r="X18">
+      <c r="X19">
         <v>108</v>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <v>126</v>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <v>144</v>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <v>162</v>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19">
-        <f>3.14157/180</f>
-        <v>1.7453166666666669E-2</v>
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="H20">
+        <f>3.14157/180</f>
+        <v>1.7453166666666669E-2</v>
+      </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
-      <c r="I21">
-        <v>5</v>
-      </c>
-      <c r="K21" s="6">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0.37675517503754502</v>
-      </c>
-      <c r="M21" s="6">
-        <v>0.92326153885340301</v>
-      </c>
-      <c r="N21" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22">
-        <v>4</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-0.91420000000000001</v>
-      </c>
-      <c r="L22" s="15">
-        <v>0.3755</v>
-      </c>
-      <c r="M22" s="15">
-        <v>0.85660000000000003</v>
+        <v>5</v>
+      </c>
+      <c r="K22" s="6">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="L22" s="6">
+        <v>0.37675517503754502</v>
+      </c>
+      <c r="M22" s="6">
+        <v>0.92326153885340301</v>
+      </c>
+      <c r="N22" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.25">
@@ -1321,45 +1381,44 @@
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23">
-        <f>I21-I22</f>
-        <v>1</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
+        <v>4</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-0.91420000000000001</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0.3755</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0.85660000000000003</v>
+      </c>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="K24" s="6">
-        <v>-1.2171799999999999</v>
-      </c>
-      <c r="L24" s="6">
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="M24" s="6">
-        <v>0.82255</v>
-      </c>
-      <c r="N24" t="s">
-        <v>32</v>
-      </c>
+      <c r="I24">
+        <f>I22-I23</f>
+        <v>1</v>
+      </c>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="K25" s="6">
-        <f>K24+K21-K22</f>
-        <v>-1.3243331220516996</v>
+        <v>-1.2171799999999999</v>
       </c>
       <c r="L25" s="6">
-        <f>L24+L21-L22</f>
-        <v>0.45175517503754498</v>
+        <v>0.45050000000000001</v>
       </c>
       <c r="M25" s="6">
-        <f>M24+M21-M22</f>
-        <v>0.88921153885340298</v>
+        <v>0.82255</v>
+      </c>
+      <c r="N25" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.25">
@@ -1367,67 +1426,95 @@
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
+      <c r="K26" s="6">
+        <f>K25+K22-K23</f>
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="L26" s="6">
+        <f>L25+L22-L23</f>
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="M26" s="6">
+        <f>M25+M22-M23</f>
+        <v>0.88921153885340298</v>
+      </c>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-      <c r="K27" s="11">
-        <v>1.2710307999999999</v>
-      </c>
-      <c r="L27" s="11">
-        <v>0.55801000000000001</v>
-      </c>
-      <c r="M27" s="11">
-        <v>1.2685808000000001</v>
-      </c>
-      <c r="N27" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-      <c r="K28" s="15">
-        <f>K27+K21-K22</f>
+      <c r="K28" s="11">
+        <v>1.2710307999999999</v>
+      </c>
+      <c r="L28" s="11">
+        <v>0.55801000000000001</v>
+      </c>
+      <c r="M28" s="11">
+        <v>1.2685808000000001</v>
+      </c>
+      <c r="N28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="K29" s="15">
+        <f>K28+K22-K23</f>
         <v>1.1638776779483</v>
       </c>
-      <c r="L28" s="15">
-        <f>L27+L21-L22</f>
+      <c r="L29" s="15">
+        <f>L28+L22-L23</f>
         <v>0.55926517503754503</v>
       </c>
-      <c r="M28" s="15">
-        <f>M27+M21-M22</f>
+      <c r="M29" s="15">
+        <f>M28+M22-M23</f>
         <v>1.3352423388534029</v>
       </c>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29" s="13"/>
-      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="H30" s="14"/>
     </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A29:A30">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+  <conditionalFormatting sqref="A30:A31">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B14">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B15">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:B28">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+  <conditionalFormatting sqref="A26:B29">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="E5 E7 E9:E15">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1440,7 +1527,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1579,441 +1666,451 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.88921153885340298</v>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="11" t="s">
-        <v>34</v>
+      <c r="H12" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="17">
-        <f t="shared" ref="H13:AB13" si="0">H18*$H$19</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R13" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB13" s="17">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+      <c r="H13" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="16">
-        <f>H16*$H$17</f>
+      <c r="H14" s="17">
+        <f t="shared" ref="H14:AB14" si="0">H19*$H$20</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R14" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB14" s="17">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="16">
+        <f>H17*$H$18</f>
         <v>-0.18</v>
       </c>
-      <c r="I14" s="16">
-        <f t="shared" ref="I14:AB14" si="1">I16*$H$17</f>
+      <c r="I15" s="16">
+        <f t="shared" ref="I15:AB15" si="1">I17*$H$18</f>
         <v>-0.1638</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J15" s="16">
         <f t="shared" si="1"/>
         <v>-0.14616000000000001</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K15" s="16">
         <f t="shared" si="1"/>
         <v>-0.12672</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L15" s="16">
         <f t="shared" si="1"/>
         <v>-0.10668000000000001</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M15" s="16">
         <f t="shared" si="1"/>
         <v>-8.7719999999999992E-2</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N15" s="16">
         <f t="shared" si="1"/>
         <v>-7.0679999999999993E-2</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O15" s="16">
         <f t="shared" si="1"/>
         <v>-5.4719999999999998E-2</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P15" s="16">
         <f t="shared" si="1"/>
         <v>-3.8159999999999999E-2</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q15" s="16">
         <f t="shared" si="1"/>
         <v>-1.9800000000000002E-2</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R15" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S15" s="16">
         <f t="shared" si="1"/>
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T15" s="16">
         <f t="shared" si="1"/>
         <v>3.8159999999999999E-2</v>
       </c>
-      <c r="U14" s="16">
+      <c r="U15" s="16">
         <f t="shared" si="1"/>
         <v>5.4719999999999998E-2</v>
       </c>
-      <c r="V14" s="16">
+      <c r="V15" s="16">
         <f t="shared" si="1"/>
         <v>7.0679999999999993E-2</v>
       </c>
-      <c r="W14" s="16">
+      <c r="W15" s="16">
         <f t="shared" si="1"/>
         <v>8.7780000000000011E-2</v>
       </c>
-      <c r="X14" s="16">
+      <c r="X15" s="16">
         <f t="shared" si="1"/>
         <v>0.10668000000000001</v>
       </c>
-      <c r="Y14" s="16">
+      <c r="Y15" s="16">
         <f t="shared" si="1"/>
         <v>0.12672</v>
       </c>
-      <c r="Z14" s="16">
+      <c r="Z15" s="16">
         <f t="shared" si="1"/>
         <v>0.14616000000000001</v>
       </c>
-      <c r="AA14" s="16">
+      <c r="AA15" s="16">
         <f t="shared" si="1"/>
         <v>0.1638</v>
       </c>
-      <c r="AB14" s="16">
+      <c r="AB15" s="16">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="11">
-        <v>-0.3</v>
-      </c>
-      <c r="I16">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J16">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K16">
-        <v>-0.2112</v>
-      </c>
-      <c r="L16">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M16">
-        <v>-0.1462</v>
-      </c>
-      <c r="N16">
-        <v>-0.1178</v>
-      </c>
-      <c r="O16">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P16">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q16">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T16">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U16">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V16">
-        <v>0.1178</v>
-      </c>
-      <c r="W16">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X16">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y16">
-        <v>0.2112</v>
-      </c>
-      <c r="Z16">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA16">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB16">
-        <v>0.3</v>
-      </c>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17">
+      <c r="H17" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="I17">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J17">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K17">
+        <v>-0.2112</v>
+      </c>
+      <c r="L17">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M17">
+        <v>-0.1462</v>
+      </c>
+      <c r="N17">
+        <v>-0.1178</v>
+      </c>
+      <c r="O17">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P17">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q17">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T17">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U17">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V17">
+        <v>0.1178</v>
+      </c>
+      <c r="W17">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X17">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y17">
+        <v>0.2112</v>
+      </c>
+      <c r="Z17">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA17">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="H18" s="11">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H19" s="11">
         <v>-180</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>-162</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>-144</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>-126</v>
       </c>
-      <c r="L18">
+      <c r="L19">
         <v>-108</v>
       </c>
-      <c r="M18">
+      <c r="M19">
         <v>-90</v>
       </c>
-      <c r="N18">
+      <c r="N19">
         <v>-72</v>
       </c>
-      <c r="O18">
+      <c r="O19">
         <v>-54</v>
       </c>
-      <c r="P18">
+      <c r="P19">
         <v>-36</v>
       </c>
-      <c r="Q18">
+      <c r="Q19">
         <v>-18</v>
       </c>
-      <c r="R18">
+      <c r="R19">
         <v>0</v>
       </c>
-      <c r="S18">
+      <c r="S19">
         <v>18</v>
       </c>
-      <c r="T18">
+      <c r="T19">
         <v>36</v>
       </c>
-      <c r="U18">
+      <c r="U19">
         <v>54</v>
       </c>
-      <c r="V18">
+      <c r="V19">
         <v>72</v>
       </c>
-      <c r="W18">
+      <c r="W19">
         <v>90</v>
       </c>
-      <c r="X18">
+      <c r="X19">
         <v>108</v>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <v>126</v>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <v>144</v>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <v>162</v>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19">
-        <f>3.14157/180</f>
-        <v>1.7453166666666669E-2</v>
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="H20">
+        <f>3.14157/180</f>
+        <v>1.7453166666666669E-2</v>
+      </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F21" s="6"/>
@@ -2036,7 +2133,6 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -2048,6 +2144,7 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -2058,31 +2155,46 @@
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29" s="13"/>
-      <c r="H29" s="14"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="H30" s="14"/>
     </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A29:A30">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+  <conditionalFormatting sqref="A30:A31">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B14">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B15">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:B28">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+  <conditionalFormatting sqref="A26:B29">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="E5 E7 E9:E15">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2095,7 +2207,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -2234,267 +2346,277 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="11">
-        <v>1.18</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0.55926517503754503</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <v>1.34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1.18</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.55926517503754503</v>
+      </c>
       <c r="H10" s="11">
-        <v>0.78888879999999995</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="22" t="s">
-        <v>34</v>
+      <c r="H12" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="16">
-        <f>H17*$H$18</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I13" s="16">
-        <f t="shared" ref="I13:AB13" si="0">I17*$H$18</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J13" s="16">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K13" s="16">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L13" s="16">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M13" s="16">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N13" s="16">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O13" s="16">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P13" s="16">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q13" s="16">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R13" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="16">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T13" s="16">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U13" s="16">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V13" s="16">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W13" s="16">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X13" s="16">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y13" s="16">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z13" s="16">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA13" s="16">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB13" s="16">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+      <c r="H13" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="16">
+        <f>H18*$H$19</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" ref="I14:AB14" si="0">I18*$H$19</f>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J14" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K14" s="16">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L14" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M14" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N14" s="16">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O14" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P14" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q14" s="16">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R14" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="16">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T14" s="16">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U14" s="16">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V14" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W14" s="16">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X14" s="16">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y14" s="16">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z14" s="16">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA14" s="16">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB14" s="16">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="16">
         <v>-0.3</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I15" s="18">
         <v>-0.27300000000000002</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J15" s="18">
         <v>-0.24360000000000001</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K15" s="18">
         <v>-0.2112</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L15" s="18">
         <v>-0.17780000000000001</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M15" s="18">
         <v>-0.1462</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N15" s="18">
         <v>-0.1178</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O15" s="18">
         <v>-9.1200000000000003E-2</v>
       </c>
-      <c r="P14" s="18">
+      <c r="P15" s="18">
         <v>-6.3600000000000004E-2</v>
       </c>
-      <c r="Q14" s="18">
+      <c r="Q15" s="18">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="R14" s="20">
+      <c r="R15" s="20">
         <v>0</v>
       </c>
-      <c r="S14" s="18">
+      <c r="S15" s="18">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="T14" s="18">
+      <c r="T15" s="18">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="U14" s="18">
+      <c r="U15" s="18">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="V14" s="18">
+      <c r="V15" s="18">
         <v>0.1178</v>
       </c>
-      <c r="W14" s="18">
+      <c r="W15" s="18">
         <v>0.14630000000000001</v>
       </c>
-      <c r="X14" s="18">
+      <c r="X15" s="18">
         <v>0.17780000000000001</v>
       </c>
-      <c r="Y14" s="18">
+      <c r="Y15" s="18">
         <v>0.2112</v>
       </c>
-      <c r="Z14" s="18">
+      <c r="Z15" s="18">
         <v>0.24360000000000001</v>
       </c>
-      <c r="AA14" s="18">
+      <c r="AA15" s="18">
         <v>0.27300000000000002</v>
       </c>
-      <c r="AB14" s="18">
+      <c r="AB15" s="18">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
@@ -2504,80 +2626,80 @@
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="11">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="11">
         <v>-180</v>
       </c>
-      <c r="I17">
+      <c r="I18">
         <v>-162</v>
       </c>
-      <c r="J17">
+      <c r="J18">
         <v>-144</v>
       </c>
-      <c r="K17">
+      <c r="K18">
         <v>-126</v>
       </c>
-      <c r="L17">
+      <c r="L18">
         <v>-108</v>
       </c>
-      <c r="M17">
+      <c r="M18">
         <v>-90</v>
       </c>
-      <c r="N17">
+      <c r="N18">
         <v>-72</v>
       </c>
-      <c r="O17">
+      <c r="O18">
         <v>-54</v>
       </c>
-      <c r="P17">
+      <c r="P18">
         <v>-36</v>
       </c>
-      <c r="Q17">
+      <c r="Q18">
         <v>-18</v>
       </c>
-      <c r="R17">
+      <c r="R18">
         <v>0</v>
       </c>
-      <c r="S17">
+      <c r="S18">
         <v>18</v>
       </c>
-      <c r="T17">
+      <c r="T18">
         <v>36</v>
       </c>
-      <c r="U17">
+      <c r="U18">
         <v>54</v>
       </c>
-      <c r="V17">
+      <c r="V18">
         <v>72</v>
       </c>
-      <c r="W17">
+      <c r="W18">
         <v>90</v>
       </c>
-      <c r="X17">
+      <c r="X18">
         <v>108</v>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <v>126</v>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <v>144</v>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <v>162</v>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="H18">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H19">
         <f>3.14157/180</f>
         <v>1.7453166666666669E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
@@ -2605,7 +2727,6 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -2617,6 +2738,7 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -2627,31 +2749,46 @@
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29" s="13"/>
-      <c r="H29" s="14"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="H30" s="14"/>
     </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A29:A30">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="A30:A31">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B14">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B15">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:B28">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+  <conditionalFormatting sqref="A26:B29">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="E5 E7 E9:E15">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2664,7 +2801,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -2804,441 +2941,451 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="15">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G9" s="15">
-        <v>-0.37675517503754502</v>
-      </c>
-      <c r="H9" s="15">
-        <v>1.2232615388534001</v>
+        <v>17</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11">
-        <v>0.35289999999999999</v>
+        <v>11</v>
+      </c>
+      <c r="F10" s="15">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G10" s="15">
+        <v>-0.37675517503754502</v>
+      </c>
+      <c r="H10" s="15">
+        <v>1.2232615388534001</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="11" t="s">
-        <v>34</v>
+      <c r="H12" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="17">
-        <f t="shared" ref="H13:AB13" si="0">H18*$H$19</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K13" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N13" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q13" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R13" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U13" s="17">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X13" s="17">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA13" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB13" s="17">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+      <c r="H13" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B14" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="16">
-        <f>H16*$H$17</f>
+      <c r="H14" s="17">
+        <f t="shared" ref="H14:AB14" si="0">H19*$H$20</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N14" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q14" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R14" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA14" s="17">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB14" s="17">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="16">
+        <f>H17*$H$18</f>
         <v>-0.18</v>
       </c>
-      <c r="I14" s="16">
-        <f t="shared" ref="I14:AB14" si="1">I16*$H$17</f>
+      <c r="I15" s="16">
+        <f t="shared" ref="I15:AB15" si="1">I17*$H$18</f>
         <v>-0.1638</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J15" s="16">
         <f t="shared" si="1"/>
         <v>-0.14616000000000001</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K15" s="16">
         <f t="shared" si="1"/>
         <v>-0.12672</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L15" s="16">
         <f t="shared" si="1"/>
         <v>-0.10668000000000001</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M15" s="16">
         <f t="shared" si="1"/>
         <v>-8.7719999999999992E-2</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N15" s="16">
         <f t="shared" si="1"/>
         <v>-7.0679999999999993E-2</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O15" s="16">
         <f t="shared" si="1"/>
         <v>-5.4719999999999998E-2</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P15" s="16">
         <f t="shared" si="1"/>
         <v>-3.8159999999999999E-2</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q15" s="16">
         <f t="shared" si="1"/>
         <v>-1.9800000000000002E-2</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R15" s="19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S15" s="16">
         <f t="shared" si="1"/>
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T15" s="16">
         <f t="shared" si="1"/>
         <v>3.8159999999999999E-2</v>
       </c>
-      <c r="U14" s="16">
+      <c r="U15" s="16">
         <f t="shared" si="1"/>
         <v>5.4719999999999998E-2</v>
       </c>
-      <c r="V14" s="16">
+      <c r="V15" s="16">
         <f t="shared" si="1"/>
         <v>7.0679999999999993E-2</v>
       </c>
-      <c r="W14" s="16">
+      <c r="W15" s="16">
         <f t="shared" si="1"/>
         <v>8.7780000000000011E-2</v>
       </c>
-      <c r="X14" s="16">
+      <c r="X15" s="16">
         <f t="shared" si="1"/>
         <v>0.10668000000000001</v>
       </c>
-      <c r="Y14" s="16">
+      <c r="Y15" s="16">
         <f t="shared" si="1"/>
         <v>0.12672</v>
       </c>
-      <c r="Z14" s="16">
+      <c r="Z15" s="16">
         <f t="shared" si="1"/>
         <v>0.14616000000000001</v>
       </c>
-      <c r="AA14" s="16">
+      <c r="AA15" s="16">
         <f t="shared" si="1"/>
         <v>0.1638</v>
       </c>
-      <c r="AB14" s="16">
+      <c r="AB15" s="16">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="11">
-        <v>-0.3</v>
-      </c>
-      <c r="I16">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J16">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K16">
-        <v>-0.2112</v>
-      </c>
-      <c r="L16">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M16">
-        <v>-0.1462</v>
-      </c>
-      <c r="N16">
-        <v>-0.1178</v>
-      </c>
-      <c r="O16">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P16">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q16">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T16">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U16">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V16">
-        <v>0.1178</v>
-      </c>
-      <c r="W16">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X16">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y16">
-        <v>0.2112</v>
-      </c>
-      <c r="Z16">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA16">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB16">
-        <v>0.3</v>
-      </c>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17">
+      <c r="H17" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="I17">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J17">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K17">
+        <v>-0.2112</v>
+      </c>
+      <c r="L17">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M17">
+        <v>-0.1462</v>
+      </c>
+      <c r="N17">
+        <v>-0.1178</v>
+      </c>
+      <c r="O17">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P17">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q17">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T17">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U17">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V17">
+        <v>0.1178</v>
+      </c>
+      <c r="W17">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X17">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y17">
+        <v>0.2112</v>
+      </c>
+      <c r="Z17">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA17">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="H18" s="11">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="H19" s="11">
         <v>-180</v>
       </c>
-      <c r="I18">
+      <c r="I19">
         <v>-162</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>-144</v>
       </c>
-      <c r="K18">
+      <c r="K19">
         <v>-126</v>
       </c>
-      <c r="L18">
+      <c r="L19">
         <v>-108</v>
       </c>
-      <c r="M18">
+      <c r="M19">
         <v>-90</v>
       </c>
-      <c r="N18">
+      <c r="N19">
         <v>-72</v>
       </c>
-      <c r="O18">
+      <c r="O19">
         <v>-54</v>
       </c>
-      <c r="P18">
+      <c r="P19">
         <v>-36</v>
       </c>
-      <c r="Q18">
+      <c r="Q19">
         <v>-18</v>
       </c>
-      <c r="R18">
+      <c r="R19">
         <v>0</v>
       </c>
-      <c r="S18">
+      <c r="S19">
         <v>18</v>
       </c>
-      <c r="T18">
+      <c r="T19">
         <v>36</v>
       </c>
-      <c r="U18">
+      <c r="U19">
         <v>54</v>
       </c>
-      <c r="V18">
+      <c r="V19">
         <v>72</v>
       </c>
-      <c r="W18">
+      <c r="W19">
         <v>90</v>
       </c>
-      <c r="X18">
+      <c r="X19">
         <v>108</v>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <v>126</v>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <v>144</v>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <v>162</v>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19">
-        <f>3.14157/180</f>
-        <v>1.7453166666666669E-2</v>
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="H20">
+        <f>3.14157/180</f>
+        <v>1.7453166666666669E-2</v>
+      </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="F21" s="6"/>
@@ -3261,7 +3408,6 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3273,6 +3419,7 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -3283,30 +3430,45 @@
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29" s="13"/>
-      <c r="H29" s="14"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="13"/>
       <c r="H30" s="14"/>
     </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A29:A30">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="A30:A31">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B14">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B15">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:B28">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="A26:B29">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E14">
+  <conditionalFormatting sqref="E5 E7:E15">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
